--- a/data/trans_bre/P15B_tráfico-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P15B_tráfico-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50,67</t>
+          <t>56,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>202,81%</t>
+          <t>410,15%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 27,65</t>
+          <t>-39,63; 26,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 19,35</t>
+          <t>-22,29; 19,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 36,14</t>
+          <t>-17,48; 32,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 85,98</t>
+          <t>8,33; 84,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,19; 69,48</t>
+          <t>-68,67; 67,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 52,67</t>
+          <t>-43,9; 55,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,3; 203,45</t>
+          <t>-51,71; 179,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-25,99</t>
+          <t>-23,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-55,46%</t>
+          <t>-54,01%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 32,06</t>
+          <t>-23,28; 33,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 27,55</t>
+          <t>-8,9; 28,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 39,56</t>
+          <t>-10,57; 37,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,08; 11,89</t>
+          <t>-54,3; 11,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,59; 176,77</t>
+          <t>-61,19; 173,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 155,54</t>
+          <t>-33,45; 155,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 239,82</t>
+          <t>-34,62; 212,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-90,18; 82,81</t>
+          <t>-100,0; 59,29</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,39</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>-1,41%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 33,23</t>
+          <t>-25,03; 36,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 12,42</t>
+          <t>-25,3; 16,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 18,58</t>
+          <t>-26,12; 21,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 26,53</t>
+          <t>-24,63; 20,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,95; 70,31</t>
+          <t>-70,8; 85,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,9; 117,08</t>
+          <t>-73,71; 147,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 125,19</t>
+          <t>-50,43; 93,36</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-15,16</t>
+          <t>-15,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-54,92%</t>
+          <t>-50,95%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 55,46</t>
+          <t>-15,28; 60,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 26,15</t>
+          <t>-4,73; 28,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 46,96</t>
+          <t>-6,55; 42,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 0,21</t>
+          <t>-30,86; 0,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,43; 854,92</t>
+          <t>-64,42; 1182,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 1097,78</t>
+          <t>-53,96; 942,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,13; 18,13</t>
+          <t>-80,2; 7,81</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,77</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-12,74%</t>
+          <t>-9,75%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-57,65; 0,0</t>
+          <t>-59,78; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 15,17</t>
+          <t>-32,36; 15,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 0,0</t>
+          <t>-46,62; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 14,43</t>
+          <t>-24,36; 13,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-92,89; —</t>
+          <t>-86,68; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 135,42</t>
+          <t>-65,9; 107,92</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>-6,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>-29,49%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-80,05; 14,94</t>
+          <t>-79,41; 12,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 7,65</t>
+          <t>-40,97; 7,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,24</t>
+          <t>0,0; 18,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 14,19</t>
+          <t>-29,33; 10,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,47; 409,94</t>
+          <t>-74,58; 141,59</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>206,38%</t>
+          <t>254,68%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-72,51; 4,74</t>
+          <t>-66,99; 4,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 5,35</t>
+          <t>-24,19; 4,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 5,93</t>
+          <t>-21,42; 5,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 9,48</t>
+          <t>-1,11; 10,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,74</t>
+          <t>-5,01</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-17,73%</t>
+          <t>-18,58%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 1,36</t>
+          <t>-23,19; 0,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,56</t>
+          <t>-13,44; 0,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 3,31</t>
+          <t>-12,87; 2,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 4,23</t>
+          <t>-13,19; 3,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 5,14</t>
+          <t>-61,33; 4,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 2,71</t>
+          <t>-47,42; 2,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,23; 21,07</t>
+          <t>-48,94; 16,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 21,59</t>
+          <t>-41,54; 18,13</t>
         </is>
       </c>
     </row>
